--- a/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
+++ b/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -548,78 +548,74 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10uF ±10% 25V X5R</t>
+          <t>10uF X5R</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C1,C18</t>
+          <t>C73,C74,C75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>C15850</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12pF 50V C0G/NP0</t>
+          <t>10uF ±10% 25V X5R</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C31,C32,C33</t>
+          <t>C1,C18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C696888</t>
+          <t>C15850</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12pF ±5% 50V C0G</t>
+          <t>12pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C31,C32,C33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C38523</t>
+          <t>C696888</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15pF ±5% 50V C0G</t>
+          <t>12pF ±5% 50V C0G</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C19,C20,C69</t>
+          <t>C68</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -629,19 +625,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C1644</t>
+          <t>C38523</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1nF ±10% 50V X7R</t>
+          <t>15pF ±5% 50V C0G</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C19,C20,C69</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -651,719 +647,695 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C1588</t>
+          <t>C1644</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1uF ±10% 25V X5R</t>
+          <t>1nF ±10% 50V X7R</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C52923</t>
+          <t>C1588</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1uF ±10% 50V X5R</t>
+          <t>1uF ±10% 25V X5R</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C2,C3,C4,C6,C28,C29,C67</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C15849</t>
+          <t>C52923</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2.7pF 50V C0G/NP0</t>
+          <t>1uF ±10% 50V X5R</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C2,C3,C4,C6,C28,C29,C67,C78,C79,C80</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C1561</t>
+          <t>C15849</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>200pF ±5% 50V NP0</t>
+          <t>2.7pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C113796</t>
+          <t>C1561</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22uF ±20% 25V X5R</t>
+          <t>200pF ±5% 50V NP0</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C60,C66</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C45783</t>
+          <t>C113796</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3.6pF 50V C0G/NP0</t>
+          <t>22uF X5R</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C40,C44</t>
+          <t>C76,C77</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>C5552081</t>
-        </is>
-      </c>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3pF 50V C0G/NP0</t>
+          <t>22uF ±20% 25V X5R</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C34,C35,C43</t>
+          <t>C60,C66</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C696883</t>
+          <t>C45783</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3pF ±0.25pF 50V C0G</t>
+          <t>3.6pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C40,C44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C46219</t>
+          <t>C5552081</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4.7uF 16V X5R</t>
+          <t>3pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C34,C35,C43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C19666</t>
+          <t>C696883</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6.2pF 50V C0G/NP0</t>
+          <t>3pF ±0.25pF 50V C0G</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C41744</t>
+          <t>C46219</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B5819W</t>
+          <t>4.7uF 16V X5R</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C15,C71</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SOD-123</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C963381</t>
+          <t>C19666</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ESD 3.3V/0.6pF</t>
+          <t>47nF 50V X7R</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D2,D3</t>
+          <t>C70</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>C2830293</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6V/200mA</t>
+          <t>6.2pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>F2,F3,F4,F5</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C516070</t>
+          <t>C41744</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TA0970A</t>
+          <t>6.8uF X5R</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FL1,FL2</t>
+          <t>C72</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SMD3838-6P</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>C7115531</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J3_HAT_2x20_SMD排针</t>
+          <t>ESD 3.3V/0.6pF</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>D2,D3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HDR-2x20_P2.54mm_SMD</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C2830293</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>U.FL_1090_EXT</t>
+          <t>6V/200mA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>F2,F3,F4,F5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IPEX-1</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C88374</t>
+          <t>C516070</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>U.FL_978</t>
+          <t>TA0970A</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>FL1,FL2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IPEX-1</t>
+          <t>SMD3838-6P</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C88374</t>
+          <t>C7115531</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>U.FL_GNSS_EXT</t>
+          <t>J3_HAT_2x20_SMD排针</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IPEX-1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>C88374</t>
-        </is>
-      </c>
+          <t>HDR-2x20_P2.54mm_SMD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>U.FL→内置patch</t>
+          <t>MX1.25WT-2P BAT</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>J8</t>
+          <t>J9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IPEX-1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>C88374</t>
-        </is>
-      </c>
+          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>USB-C_16P</t>
+          <t>U.FL_1090_EXT</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TYPE-C-31-M-12</t>
+          <t>IPEX-1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C165948</t>
+          <t>C88374</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>U.FL_978</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>L8,L14</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>IPEX-1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C18221115</t>
+          <t>C88374</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>27nH</t>
+          <t>U.FL_GNSS_EXT</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>L10</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>IPEX-1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C7519921</t>
+          <t>C88374</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>U.FL_IFA_TEST</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>L2,L15</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>IPEX-1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C6807986</t>
+          <t>C88374</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6.8nH</t>
+          <t>U.FL→内置patch</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>L11,L12</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>IPEX-1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C82919</t>
+          <t>C88374</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6.8uH</t>
+          <t>USB-C_16P</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>TYPE-C-31-M-12</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C82157</t>
+          <t>C165948</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>1.5uH</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>L9,L13</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>C82918</t>
-        </is>
-      </c>
+          <t>L_Bourns-SRN4018</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Q2,Q3,Q4,Q5</t>
+          <t>L8,L14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C347476</t>
+          <t>C18221115</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0R ±1% 100mW</t>
+          <t>1uH</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>R22,R23,ZS1</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>C21189</t>
-        </is>
-      </c>
+          <t>L_Bourns-SRN4018</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>100k ±1% 100mW</t>
+          <t>27nH</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C25803</t>
+          <t>C7519921</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10k ±1% 100mW</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>R1,R5,R6,R17,R18,R26,R27,R32,R34,R35</t>
+          <t>L2,L15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C25804</t>
+          <t>C6807986</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>18k ±1% 100mW</t>
+          <t>6.8nH</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>L11,L12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C25810</t>
+          <t>C82919</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1k ±1% 100mW</t>
+          <t>6.8uH</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>R4,R31,R36</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C21190</t>
+          <t>C82157</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1k ±1% 62.5mW</t>
+          <t>7.5nH</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>L9,L13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1373,41 +1345,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C82918</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27R ±1% 100mW</t>
+          <t>AO3401A</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>R9,R10</t>
+          <t>Q2,Q3,Q4,Q5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C25190</t>
+          <t>C347476</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4.7k ±1% 100mW</t>
+          <t>0R ±1% 100mW</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>R2,R3</t>
+          <t>R22,R23,ZS1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1417,19 +1389,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C23162</t>
+          <t>C21189</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5.1k ±1% 100mW</t>
+          <t>100k ±1% 100mW</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>R7,R8</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1439,401 +1411,725 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C23186</t>
+          <t>C25803</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>52.3R</t>
+          <t>10k ±1% 100mW</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R1,R5,R6,R17,R18,R26,R27,R32,R34,R35,R44,R45,R46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C273696</t>
+          <t>C25804</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AD8319ACPZ-R7</t>
+          <t>150k</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LFCSP-8_3x2mm_P0.5mm</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>C21652</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ATGM336H-6N-74</t>
+          <t>180R</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>R38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LCC-18_10.1x9.7mm</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>C5804601</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BGA2817</t>
+          <t>18k ±1% 100mW</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SOT-363</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C2654187</t>
+          <t>C25810</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BMP388</t>
+          <t>1k ±1% 100mW</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>R4,R31,R36,R43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LGA-10_2x2mm_P0.5mm</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>C779278</t>
+          <t>C21190</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BNO085</t>
+          <t>1k ±1% 62.5mW</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LGA-28_3.8x5.2mm_P0.5mm</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>C5189642</t>
+          <t>C11702</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CC1312R1F3RGZR</t>
+          <t>27R ±1% 100mW</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>R9,R10</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>QFN-48_7x7mm_P0.5mm</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>C543014</t>
+          <t>C25190</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ME6211C33M5</t>
+          <t>31.6k</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>C82942</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QMC5883P</t>
+          <t>4.7k ±1% 100mW</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>R2,R3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LGA-16_3x3mm_P0.5mm</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>C2847467</t>
+          <t>C23162</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QPL9547TR7</t>
+          <t>470k</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DFN-8_2x2mm_P0.5mm</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>C5367093</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RP2040</t>
+          <t>5.62k</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>R39</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>QFN-56_7x7mm_P0.4mm</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>C2040</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TLV3501</t>
+          <t>52.3R</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>U15</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>C54582190</t>
+          <t>C273696</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>6.8k</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>U2,U3</t>
+          <t>R37</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>C2862740</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>W25Q128JVSIQ</t>
+          <t>103AT-2 10k NTC</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>RT1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SOIC-8_208mil</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>C97521</t>
-        </is>
-      </c>
+          <t>NTC_103AT-2_Leaded_P2.54mm</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>XA17-G4K</t>
+          <t>AD8319ACPZ-R7</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>U16,U17</t>
+          <t>U13</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SOT-363</t>
+          <t>LFCSP-8_3x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>C513494</t>
+          <t>C21652</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12MHz</t>
+          <t>ATGM336H-6N-74</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Y1</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SMD3225-4P</t>
+          <t>LCC-18_10.1x9.7mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>C9002</t>
+          <t>C5804601</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>32.768kHz FC-135</t>
+          <t>BGA2817</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Y3</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SMD3215-2P</t>
+          <t>SOT-363</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>C32346</t>
+          <t>C2654187</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>BMP388</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>LGA-10_2x2mm_P0.5mm</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>C779278</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BNO085</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>LGA-28_3.8x5.2mm_P0.5mm</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>C5189642</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CC1312R1F3RGZR</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>QFN-48_7x7mm_P0.5mm</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>C543014</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CH224K</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>U18</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CH224K_ESSOP-10</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>C970725</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ME6211C33M5</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SOT-23-5</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>C82942</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QMC5883P</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>LGA-16_3x3mm_P0.5mm</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>C2847467</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QPL9547TR7</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DFN-8_2x2mm_P0.5mm</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>C5367093</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>RP2040</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>QFN-56_7x7mm_P0.4mm</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>C2040</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SY6970</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>U19</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>C5357542</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SY7069</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>U20</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>TSOT-23-6</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>淘宝（立创未见）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TLV3501</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>U15</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SOT-23-6</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>C54582190</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TPS7A2033PDBVR</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>U2,U3</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SOT-23-5</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>C2862740</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>W25Q128JVSIQ</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SOIC-8_208mil</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>C97521</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>XA17-G4K</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>U16,U17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SOT-363</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>C513494</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>12MHz</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SMD3225-4P</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>C9002</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>32.768kHz FC-135</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SMD3215-2P</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>C32346</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>48MHz ABM8W-7pF</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>SMD3225-4P</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>C6732653</t>
         </is>

--- a/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
+++ b/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
@@ -1680,7 +1680,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>103AT-2 10k NTC</t>
+          <t>NCP18XH103F03RB 10k NTC</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NTC_103AT-2_Leaded_P2.54mm</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>

--- a/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
+++ b/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
@@ -548,74 +548,78 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10uF X5R</t>
+          <t>10uF ±10% 25V X5R</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C73,C74,C75</t>
+          <t>C1,C18,C73,C74,C75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C15850</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10uF ±10% 25V X5R</t>
+          <t>12pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C1,C18</t>
+          <t>C31,C32,C33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C15850</t>
+          <t>C696888</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12pF 50V C0G/NP0</t>
+          <t>12pF ±5% 50V C0G</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C31,C32,C33</t>
+          <t>C68</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C696888</t>
+          <t>C38523</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12pF ±5% 50V C0G</t>
+          <t>15pF ±5% 50V C0G</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C19,C20,C69</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -625,19 +629,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C38523</t>
+          <t>C1644</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15pF ±5% 50V C0G</t>
+          <t>1nF ±10% 50V X7R</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C19,C20,C69</t>
+          <t>C51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -647,169 +651,169 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C1644</t>
+          <t>C1588</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1nF ±10% 50V X7R</t>
+          <t>1uF ±10% 25V X5R</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C1588</t>
+          <t>C52923</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1uF ±10% 25V X5R</t>
+          <t>1uF ±10% 50V X5R</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C2,C3,C4,C6,C28,C29,C67,C78,C79,C80</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C52923</t>
+          <t>C15849</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1uF ±10% 50V X5R</t>
+          <t>2.7pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>C2,C3,C4,C6,C28,C29,C67,C78,C79,C80</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C15849</t>
+          <t>C1561</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2.7pF 50V C0G/NP0</t>
+          <t>200pF ±5% 50V NP0</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C41</t>
+          <t>C47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1561</t>
+          <t>C113796</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>200pF ±5% 50V NP0</t>
+          <t>22uF X5R</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C76,C77</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>C113796</t>
-        </is>
-      </c>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22uF X5R</t>
+          <t>22uF ±20% 25V X5R</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C76,C77</t>
+          <t>C60,C66</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C45783</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22uF ±20% 25V X5R</t>
+          <t>3.6pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C60,C66</t>
+          <t>C40,C44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C45783</t>
+          <t>C5552081</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3.6pF 50V C0G/NP0</t>
+          <t>3pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C40,C44</t>
+          <t>C34,C35,C43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -819,41 +823,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5552081</t>
+          <t>C696883</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3pF 50V C0G/NP0</t>
+          <t>3pF ±0.25pF 50V C0G</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C34,C35,C43</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C696883</t>
+          <t>C46219</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3pF ±0.25pF 50V C0G</t>
+          <t>4.7uF 16V X5R</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C15,C71</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -863,19 +867,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C46219</t>
+          <t>C19666</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4.7uF 16V X5R</t>
+          <t>47nF 50V X7R</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C15,C71</t>
+          <t>C70</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -883,150 +887,146 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>C19666</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>47nF 50V X7R</t>
+          <t>6.2pF 50V C0G/NP0</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C70</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C41744</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6.2pF 50V C0G/NP0</t>
+          <t>6.8uF X5R</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C72</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>C41744</t>
-        </is>
-      </c>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6.8uF X5R</t>
+          <t>ESD 3.3V/0.6pF</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C72</t>
+          <t>D2,D3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C2830293</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ESD 3.3V/0.6pF</t>
+          <t>6V/200mA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D2,D3</t>
+          <t>F2,F3,F4,F5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C2830293</t>
+          <t>C516070</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6V/200mA</t>
+          <t>TA0970A</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>F2,F3,F4,F5</t>
+          <t>FL1,FL2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>SMD3838-6P</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C516070</t>
+          <t>C7115531</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TA0970A</t>
+          <t>J3_HAT_2x20_SMD排针</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FL1,FL2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SMD3838-6P</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>C7115531</t>
-        </is>
-      </c>
+          <t>HDR-2x20_P2.54mm_SMD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>J3_HAT_2x20_SMD排针</t>
+          <t>MX1.25WT-2P BAT</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HDR-2x20_P2.54mm_SMD</t>
+          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1034,30 +1034,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P BAT</t>
+          <t>U.FL_1090_EXT</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>J9</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MX1.25WT-2P_1x02-1MP_P1.25mm_Horizontal</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>IPEX-1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C88374</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>U.FL_1090_EXT</t>
+          <t>U.FL_978</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1074,12 +1078,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>U.FL_978</t>
+          <t>U.FL_GNSS_EXT</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1096,12 +1100,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>U.FL_GNSS_EXT</t>
+          <t>U.FL_IFA_TEST</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1118,12 +1122,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>U.FL_IFA_TEST</t>
+          <t>U.FL→内置patch</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>J7</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1140,114 +1144,114 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>U.FL→内置patch</t>
+          <t>USB-C_16P</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>J8</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IPEX-1</t>
+          <t>TYPE-C-31-M-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C88374</t>
+          <t>C165948</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>USB-C_16P</t>
+          <t>1.5uH</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TYPE-C-31-M-12</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>C165948</t>
-        </is>
-      </c>
+          <t>L_Bourns-SRN4018</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1.5uH</t>
+          <t>100nH</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>L8,L14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>L_Bourns-SRN4018</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>C18221115</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>100nH</t>
+          <t>1uH</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>L8,L14</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>C18221115</t>
-        </is>
-      </c>
+          <t>L_Bourns-SRN4018</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1uH</t>
+          <t>27nH</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>L16</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>L_Bourns-SRN4018</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C7519921</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27nH</t>
+          <t>33nH</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>L10</t>
+          <t>L2,L15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1257,19 +1261,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C7519921</t>
+          <t>C6807986</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>33nH</t>
+          <t>6.8nH</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>L2,L15</t>
+          <t>L11,L12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1279,107 +1283,107 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C6807986</t>
+          <t>C82919</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6.8nH</t>
+          <t>6.8uH</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>L11,L12</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C82919</t>
+          <t>C82157</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6.8uH</t>
+          <t>7.5nH</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L9,L13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C82157</t>
+          <t>C82918</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7.5nH</t>
+          <t>AO3401A</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>L9,L13</t>
+          <t>Q2,Q3,Q4,Q5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C82918</t>
+          <t>C347476</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>0R ±1% 100mW</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Q2,Q3,Q4,Q5</t>
+          <t>R22,R23,ZS1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C347476</t>
+          <t>C21189</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0R ±1% 100mW</t>
+          <t>100k ±1% 100mW</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>R22,R23,ZS1</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1389,19 +1393,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C21189</t>
+          <t>C25803</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>100k ±1% 100mW</t>
+          <t>10k ±1% 100mW</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R1,R5,R6,R17,R18,R26,R27,R32,R34,R35,R44,R45,R46</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1411,19 +1415,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C25803</t>
+          <t>C25804</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10k ±1% 100mW</t>
+          <t>150k</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>R1,R5,R6,R17,R18,R26,R27,R32,R34,R35,R44,R45,R46</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1431,21 +1435,17 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>C25804</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>150k</t>
+          <t>180R</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1458,12 +1458,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>180R</t>
+          <t>18k ±1% 100mW</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>R38</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1471,17 +1471,21 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C25810</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18k ±1% 100mW</t>
+          <t>1k ±1% 100mW</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R4,R31,R36,R43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1491,63 +1495,63 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C25810</t>
+          <t>C21190</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1k ±1% 100mW</t>
+          <t>1k ±1% 62.5mW</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>R4,R31,R36,R43</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>C21190</t>
+          <t>C11702</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1k ±1% 62.5mW</t>
+          <t>27R ±1% 100mW</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>R9,R10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C25190</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27R ±1% 100mW</t>
+          <t>31.6k</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>R9,R10</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1555,21 +1559,17 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>C25190</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>31.6k</t>
+          <t>4.7k ±1% 100mW</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R2,R3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1577,17 +1577,21 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>C23162</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4.7k ±1% 100mW</t>
+          <t>470k</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>R2,R3</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1595,21 +1599,17 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>C23162</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>470k</t>
+          <t>5.1k ±1% 100mW</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R7,R8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1617,7 +1617,11 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>C23186</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">

--- a/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
+++ b/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>R22,R23,ZS1</t>
+          <t>R21,R22,R23,ZS1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1458,12 +1458,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>18k ±1% 100mW</t>
+          <t>1k ±1% 100mW</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R4,R31,R36,R43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1473,63 +1473,63 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C25810</t>
+          <t>C21190</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1k ±1% 100mW</t>
+          <t>1k ±1% 62.5mW</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>R4,R31,R36,R43</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C21190</t>
+          <t>C11702</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1k ±1% 62.5mW</t>
+          <t>27R ±1% 100mW</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>R9,R10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C25190</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27R ±1% 100mW</t>
+          <t>31.6k</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>R9,R10</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1537,21 +1537,17 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>C25190</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>31.6k</t>
+          <t>4.7k ±1% 100mW</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R2,R3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1559,17 +1555,21 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>C23162</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4.7k ±1% 100mW</t>
+          <t>470k</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>R2,R3</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1577,21 +1577,17 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>C23162</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>470k</t>
+          <t>5.1k ±1% 100mW</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R7,R8</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1599,17 +1595,21 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>C23186</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5.1k ±1% 100mW</t>
+          <t>5.62k</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>R7,R8</t>
+          <t>R39</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1617,61 +1617,57 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>C23186</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5.62k</t>
+          <t>52.3R</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>R39</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>C273696</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>52.3R</t>
+          <t>6.8k</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R37</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>C273696</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6.8k</t>
+          <t>NCP18XH103F03RB 10k NTC</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>R37</t>
+          <t>RT1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1684,456 +1680,438 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NCP18XH103F03RB 10k NTC</t>
+          <t>AD8313ARMZ</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>RT1</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>MSOP-8_3x3mm_P0.65mm</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>C578690</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AD8319ACPZ-R7</t>
+          <t>ATGM336H-6N-74</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LFCSP-8_3x2mm_P0.5mm</t>
+          <t>LCC-18_10.1x9.7mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>C21652</t>
+          <t>C5804601</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ATGM336H-6N-74</t>
+          <t>BGA2817</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LCC-18_10.1x9.7mm</t>
+          <t>SOT-363</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>C5804601</t>
+          <t>C2654187</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BGA2817</t>
+          <t>BMP388</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SOT-363</t>
+          <t>LGA-10_2x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>C2654187</t>
+          <t>C779278</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BMP388</t>
+          <t>BNO085</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LGA-10_2x2mm_P0.5mm</t>
+          <t>LGA-28_3.8x5.2mm_P0.5mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>C779278</t>
+          <t>C5189642</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BNO085</t>
+          <t>CC1312R1F3RGZR</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LGA-28_3.8x5.2mm_P0.5mm</t>
+          <t>QFN-48_7x7mm_P0.5mm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>C5189642</t>
+          <t>C543014</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CC1312R1F3RGZR</t>
+          <t>CH224K</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>QFN-48_7x7mm_P0.5mm</t>
+          <t>CH224K_ESSOP-10</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>C543014</t>
+          <t>C970725</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CH224K</t>
+          <t>ME6211C33M5</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CH224K_ESSOP-10</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>C970725</t>
+          <t>C82942</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ME6211C33M5</t>
+          <t>QMC5883P</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>LGA-16_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>C82942</t>
+          <t>C2847467</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QMC5883P</t>
+          <t>QPL9547TR7</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LGA-16_3x3mm_P0.5mm</t>
+          <t>DFN-8_2x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>C2847467</t>
+          <t>C5367093</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QPL9547TR7</t>
+          <t>RP2040</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DFN-8_2x2mm_P0.5mm</t>
+          <t>QFN-56_7x7mm_P0.4mm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>C5367093</t>
+          <t>C2040</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RP2040</t>
+          <t>SY6970</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>QFN-56_7x7mm_P0.4mm</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>C2040</t>
+          <t>C5357542</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SY6970</t>
+          <t>SY7069</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>U19</t>
+          <t>U20</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm_ThermalVias</t>
+          <t>TSOT-23-6</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>C5357542</t>
+          <t>淘宝（立创未见）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SY7069</t>
+          <t>TLV3501</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>U20</t>
+          <t>U15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TSOT-23-6</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>淘宝（立创未见）</t>
+          <t>C54582190</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TLV3501</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>U15</t>
+          <t>U2,U3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>C54582190</t>
+          <t>C2862740</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>W25Q128JVSIQ</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>U2,U3</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>SOIC-8_208mil</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C2862740</t>
+          <t>C97521</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>W25Q128JVSIQ</t>
+          <t>XA17-G4K</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U16,U17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SOIC-8_208mil</t>
+          <t>SOT-363</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>C97521</t>
+          <t>C513494</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>XA17-G4K</t>
+          <t>12MHz</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>U16,U17</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SOT-363</t>
+          <t>SMD3225-4P</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>C513494</t>
+          <t>C9002</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>12MHz</t>
+          <t>32.768kHz FC-135</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Y1</t>
+          <t>Y3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SMD3225-4P</t>
+          <t>SMD3215-2P</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>C9002</t>
+          <t>C32346</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>32.768kHz FC-135</t>
+          <t>48MHz ABM8W-7pF</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Y3</t>
+          <t>Y2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SMD3215-2P</t>
+          <t>SMD3225-4P</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
-        <is>
-          <t>C32346</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>48MHz ABM8W-7pF</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>SMD3225-4P</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
         <is>
           <t>C6732653</t>
         </is>

--- a/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
+++ b/hardware/expansion-board-v4/BOM_嘉立创SMT.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
